--- a/Testdata/SingleOrganizationTestData.xlsx
+++ b/Testdata/SingleOrganizationTestData.xlsx
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Organization ID</t>
   </si>
   <si>
-    <t xml:space="preserve">Test_RE_Demo_0202_organization</t>
+    <t xml:space="preserve">Test_RE_Demo_0203_organization</t>
   </si>
   <si>
     <t xml:space="preserve">Organization Title</t>
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Email</t>
   </si>
   <si>
-    <t xml:space="preserve">Testorgz01@yopmail.com</t>
+    <t xml:space="preserve">testdeldistrictre13@yopmail.com</t>
   </si>
   <si>
     <t xml:space="preserve">Support Admin</t>
@@ -74,7 +74,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -123,6 +123,13 @@
       <sz val="10"/>
       <color rgb="FF0563C1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -208,7 +215,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -216,7 +223,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -555,7 +562,7 @@
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" display="Testorgz01@yopmail.com"/>
+    <hyperlink ref="B7" r:id="rId1" display="testdeldistrictre13@yopmail.com"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Testdata/SingleOrganizationTestData.xlsx
+++ b/Testdata/SingleOrganizationTestData.xlsx
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Organization ID</t>
   </si>
   <si>
-    <t xml:space="preserve">Test_RE_Demo_0203_organization</t>
+    <t xml:space="preserve">Test_RE_Demo_0205_organization</t>
   </si>
   <si>
     <t xml:space="preserve">Organization Title</t>
@@ -46,19 +46,19 @@
     <t xml:space="preserve">First Name</t>
   </si>
   <si>
-    <t xml:space="preserve">testfirst0202</t>
+    <t xml:space="preserve">testfirst0205</t>
   </si>
   <si>
     <t xml:space="preserve">Last Name</t>
   </si>
   <si>
-    <t xml:space="preserve">testlast0202</t>
+    <t xml:space="preserve">testlast0205</t>
   </si>
   <si>
     <t xml:space="preserve">Email</t>
   </si>
   <si>
-    <t xml:space="preserve">testdeldistrictre13@yopmail.com</t>
+    <t xml:space="preserve">testdeldistrict15@yopmail.com</t>
   </si>
   <si>
     <t xml:space="preserve">Support Admin</t>
@@ -128,15 +128,15 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -190,7 +190,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -215,7 +215,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -223,8 +223,12 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -559,10 +563,16 @@
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="8"/>
     </row>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="0"/>
+    </row>
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="9"/>
+    </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" display="testdeldistrictre13@yopmail.com"/>
+    <hyperlink ref="B7" r:id="rId1" display="testdeldistrict15@yopmail.com"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Testdata/SingleOrganizationTestData.xlsx
+++ b/Testdata/SingleOrganizationTestData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="7"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21990" windowHeight="4800" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="SingleOG" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="SingleOG" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -22,83 +22,64 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
-    <t xml:space="preserve">Field Names</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organization ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test_RE_Demo_0205_organization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organization Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">State</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Florida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testfirst0205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Last Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testlast0205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">testdeldistrict15@yopmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Admin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunil Game</t>
+    <t>Field Names</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Organization ID</t>
+  </si>
+  <si>
+    <t>Organization Title</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>Florida</t>
+  </si>
+  <si>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>Last Name</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Support Admin</t>
+  </si>
+  <si>
+    <t>Sunil Game</t>
+  </si>
+  <si>
+    <t>Test_RE_Demo_0213_organization</t>
+  </si>
+  <si>
+    <t>testfirst0213</t>
+  </si>
+  <si>
+    <t>testlast0213</t>
+  </si>
+  <si>
+    <t>testdeldistrict13@yopmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="10">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -109,7 +90,6 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -138,6 +118,13 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -150,96 +137,61 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -298,13 +250,29 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -346,14 +314,14 @@
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -383,7 +351,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -407,7 +375,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -467,28 +435,29 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
     <outlinePr summaryBelow="0"/>
-    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C1048576"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="35.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34.29"/>
+    <col min="1" max="1" width="35.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="34.28515625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -497,89 +466,84 @@
       </c>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3"/>
-    </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="B3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="3"/>
-    </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="3"/>
-    </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="B5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="3"/>
-    </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="B7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B8" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="3"/>
-    </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="3"/>
-    </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>14</v>
-      </c>
       <c r="C8" s="3"/>
     </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8"/>
-    </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0"/>
-    </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="9"/>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="7"/>
+    </row>
+    <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11"/>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="8"/>
+    </row>
+    <row r="1048576" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" display="testdeldistrict15@yopmail.com"/>
+    <hyperlink ref="B7" r:id="rId1"/>
   </hyperlinks>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>